--- a/public/firm-onboarding-guides/client-list-template.xlsx
+++ b/public/firm-onboarding-guides/client-list-template.xlsx
@@ -258,7 +258,7 @@
     <t>Unknown means you are not sure. Mark it Unknown and the client stays out of the send until the basis is confirmed.</t>
   </si>
   <si>
-    <t>The safe first send is everyone marked Express, plus Implied clients whose matter closed within the last two years. For matters that closed in 2024, check the actual month, since the two-year window falls in mid-2024. Anyone whose matter closed before that, with no express consent, should not receive marketing email.</t>
+    <t>The safe first send is everyone marked Express, plus Implied clients whose matter closed within the last two years. Count back exactly two years from the current date; for matters that closed in that boundary year, check the actual month. Anyone whose matter closed before that, with no express consent, should not receive marketing email.</t>
   </si>
 </sst>
 </file>
